--- a/search_form/input/summer.xlsx
+++ b/search_form/input/summer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Medoctor\_internal\search_form\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A3E229-5FC7-4E93-BCBD-E1C0CBD44F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F56632F-041B-4389-9A0E-7FC59C1C4A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -894,7 +894,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="7">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="C12" t="str">
         <f>IF(ISERROR(MATCH(A12,Sheet1!A:A,0))," ","+")</f>
@@ -1578,7 +1578,7 @@
         <v>48</v>
       </c>
       <c r="B69" s="7">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C69" t="str">
         <f>IF(ISERROR(MATCH(A69,Sheet1!B:B,0))," ","+")</f>
